--- a/output/前橋赤十字病院_随意契約_X線関連.xlsx
+++ b/output/前橋赤十字病院_随意契約_X線関連.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -671,7 +671,7 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2023年度（2023年6月8日〜2024年1月29日）</t>
+          <t>2023年度（2023年4月10日〜2024年3月29日）</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -680,25 +680,55 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2024年度（2024年4月1日〜2024年9月20日）</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>https://www.maebashi.jrc.or.jp/other/pdf/2024up.pdf</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>・出典: 前橋赤十字病院「入札情報」ページ https://www.maebashi.jrc.or.jp/other/bidding.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>・調査範囲は2023〜2025年度の公表分。</t>
-        </is>
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>2024年度・2025年度（2025年1月9日〜2025年9月17日）</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>https://www.maebashi.jrc.or.jp/other/pdf/2025.pdf</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>・出典: 前橋赤十字病院「入札情報」ページ https://www.maebashi.jrc.or.jp/other/bidding.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>・調査範囲は2023〜2025年度の公表分。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>・公表対象は日本赤十字社会計規則に基づく随意契約のみ。競争入札による調達は含まれない。</t>
         </is>
